--- a/Result/profitability/3118.xlsx
+++ b/Result/profitability/3118.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5775</v>
+        <v>0.5725</v>
       </c>
       <c r="N2" t="n">
-        <v>35.13375</v>
+        <v>35.3025</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.84</v>
       </c>
       <c r="M3" t="n">
-        <v>0.625</v>
+        <v>0.6024999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>36.2875</v>
+        <v>36.52375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.37</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5962499999999999</v>
+        <v>0.5725</v>
       </c>
       <c r="N4" t="n">
-        <v>36.94</v>
+        <v>37.27875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5625</v>
+        <v>0.55875</v>
       </c>
       <c r="N5" t="n">
-        <v>37.81125</v>
+        <v>37.67875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.49875</v>
       </c>
       <c r="N6" t="n">
-        <v>37.86875000000001</v>
+        <v>37.29875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4712499999999999</v>
+        <v>0.4525</v>
       </c>
       <c r="N7" t="n">
-        <v>37.36625</v>
+        <v>37.22875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.45625</v>
+        <v>0.4424999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>37.64625</v>
+        <v>37.19875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3118</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>162</v>
+      </c>
+      <c r="D75" t="n">
+        <v>107</v>
+      </c>
+      <c r="E75" t="n">
+        <v>55</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="G75" t="n">
+        <v>12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.37%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>16</v>
+      </c>
+      <c r="K75" t="n">
+        <v>14</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.55875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.41375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2075471698113208</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.580000000000005</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0955941255006677</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.06666666666666676</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.060000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03034640709991421</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
